--- a/表格/身高统计买文化衫0616.xlsx
+++ b/表格/身高统计买文化衫0616.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ants\Desktop\社会实践\表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE79589-8474-442B-93CA-B41512BA930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C0581-240B-4938-BE2F-B5571DA0C1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="81">
   <si>
     <t>序号</t>
   </si>
@@ -31,6 +31,9 @@
     <t>2、您的身高（单位：厘米）</t>
   </si>
   <si>
+    <t>3、性别</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>185</t>
   </si>
   <si>
+    <t>男</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -58,6 +64,9 @@
     <t>168</t>
   </si>
   <si>
+    <t>女</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
@@ -251,6 +260,10 @@
   </si>
   <si>
     <t>孙晟哲</t>
+  </si>
+  <si>
+    <t>女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -293,8 +306,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -634,16 +648,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.69921875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
     <col min="3" max="3" width="11.69921875" customWidth="1"/>
-    <col min="4" max="26" width="16.69921875" customWidth="1"/>
+    <col min="4" max="26" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,336 +667,423 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="16" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="18" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="D27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C29 A30:C30 A31:C31" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>